--- a/extenbooks/XS1305.xlsx
+++ b/extenbooks/XS1305.xlsx
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-06): With E2 excluded from NSW computation (standard Shaikh-Tonak/Moos formula), ST2 P21 produces a structural shift of +0.054 across the 2000-2001 boundary (mean post-2000 minus mean pre-2000 for NSW/EC), compared to a structural shift of +0.030 in NSW/EC implied by Moos's published data. For NSW/GDP the analogous comparison: ST2 mean 1959-1997 = 0.013 vs Moos published 0.011. The structural shift is larger in ST2 than in Moos — attributable to NIPA vintage differences (2026 pull vs ~2015 pull).</t>
+          <t>[internal-decision-record] (2026-05-06): With E2 excluded from NSW computation (standard Shaikh-Tonak/Moos formula), predecessor-build P21 produces a structural shift of +0.054 across the 2000-2001 boundary (mean post-2000 minus mean pre-2000 for NSW/EC), compared to a structural shift of +0.030 in NSW/EC implied by Moos's published data. For NSW/GDP the analogous comparison: predecessor-build mean 1959-1997 = 0.013 vs Moos published 0.011. The structural shift is larger in predecessor-build than in Moos — attributable to NIPA vintage differences (2026 pull vs ~2015 pull).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>series_registry.json XS1305 validation reference_values: structural_shift = 0.030. This is the Moos-published magnitude of the post-2000 mean shift in NSW/EC. ST2 achieves structural_shift = 0.054 ([internal-decision-record]), which is larger due to NIPA vintage. Expected range for XS1305 is [-0.05, 0.10] for NSW/GDP values. The V11 validator should confirm: (1) pre-2000 mean approximately zero; (2) post-2000 mean substantially positive; (3) shift magnitude in plausible range.</t>
+          <t>series_registry.json XS1305 validation reference_values: structural_shift = 0.030. This is the Moos-published magnitude of the post-2000 mean shift in NSW/EC. predecessor-build achieves structural_shift = 0.054 ([internal-decision-record]), which is larger due to NIPA vintage. Expected range for XS1305 is [-0.05, 0.10] for NSW/GDP values. The V11 validator should confirm: (1) pre-2000 mean approximately zero; (2) post-2000 mean substantially positive; (3) shift magnitude in plausible range.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XS1305 is XS1301 with post-2000 regime indicator added. Quantifies the structural break in NSW/GDP identified by Moos (2017) as the main contribution of her paper. Published structural shift = 0.030 (NSW/EC); ST2 achieves 0.054 (larger, NIPA vintage effect). Pre-2000 mean ~0%; post-2000 mean ~5% GDP. Caused by combination of income support growth, healthcare inflation, neoliberal tax cuts, and unprecedented unemployment intensity during Great Recession.</t>
+          <t>XS1305 is XS1301 with post-2000 regime indicator added. Quantifies the structural break in NSW/GDP identified by Moos (2017) as the main contribution of her paper. Published structural shift = 0.030 (NSW/EC); predecessor-build achieves 0.054 (larger, NIPA vintage effect). Pre-2000 mean ~0%; post-2000 mean ~5% GDP. Caused by combination of income support growth, healthcare inflation, neoliberal tax cuts, and unprecedented unemployment intensity during Great Recession.</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ST2 structural shift of +0.054 exceeds Moos published +0.030; difference attributable to NIPA vintage (2026 vs ~2015 pull)</t>
+          <t>predecessor-build structural shift of +0.054 exceeds Moos published +0.030; difference attributable to NIPA vintage (2026 vs ~2015 pull)</t>
         </is>
       </c>
     </row>
